--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -94,6 +94,36 @@
     <t>12/09/2026 22:00:00</t>
   </si>
   <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>Sai giờ</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>02222350</t>
   </si>
   <si>
@@ -103,28 +133,10 @@
     <t>Tăng cường sản xuất</t>
   </si>
   <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
-  </si>
-  <si>
-    <t>Sai giờ</t>
-  </si>
-  <si>
-    <t>Từ chối</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
   </si>
   <si>
     <t>19/09/2026 22:00:00</t>
@@ -139,18 +151,45 @@
     <t>24/09/2026 14:00:00</t>
   </si>
   <si>
-    <t>21/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
     <t>23/09/2026 16:30:00</t>
   </si>
   <si>
@@ -160,13 +199,19 @@
     <t>chuẩn bị kiểm kê</t>
   </si>
   <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>lắp đặt thiết bị</t>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
   </si>
   <si>
     <t>02223605</t>
@@ -175,37 +220,25 @@
     <t>Võ Minh Bắc</t>
   </si>
   <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
     <t>13/09/2026 06:00:00</t>
   </si>
   <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>23/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
   </si>
   <si>
     <t>22/09/2026 12:30:00</t>
@@ -214,30 +247,6 @@
     <t>22/09/2026 14:00:00</t>
   </si>
   <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>02644075</t>
   </si>
   <si>
@@ -253,6 +262,57 @@
     <t xml:space="preserve">tăng cường sản xuất </t>
   </si>
   <si>
+    <t>24/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>02243654</t>
   </si>
   <si>
@@ -262,48 +322,12 @@
     <t>Tăng Cường Sản Xuất</t>
   </si>
   <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>02622116</t>
   </si>
   <si>
     <t>Trịnh Nhựt Khánh</t>
   </si>
   <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>02644066</t>
   </si>
   <si>
@@ -313,43 +337,37 @@
     <t>tang ca van hanh may nghien</t>
   </si>
   <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
     <t>15/09/2026 12:30:00</t>
   </si>
   <si>
     <t xml:space="preserve">tang ca cat ong nhua </t>
   </si>
   <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 22:00:00</t>
   </si>
 </sst>
 </file>
@@ -898,13 +916,13 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G5" s="8">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>19</v>
@@ -913,49 +931,49 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="L5" s="8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="8">
+        <v>90</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="8">
-        <v>435</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
@@ -972,13 +990,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G7" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>19</v>
@@ -987,7 +1005,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -996,10 +1014,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
@@ -1008,13 +1026,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G8" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>19</v>
@@ -1023,7 +1041,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1032,34 +1050,34 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="8">
+        <v>90</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="8">
-        <v>480</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1068,34 +1086,34 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="8">
+        <v>480</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="8">
-        <v>90</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -1104,34 +1122,34 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="8">
+        <v>480</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="8">
-        <v>90</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1140,23 +1158,23 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="G12" s="8">
         <v>90</v>
       </c>
@@ -1167,7 +1185,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1176,10 +1194,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1188,13 +1206,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G13" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>19</v>
@@ -1203,7 +1221,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1212,10 +1230,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1224,10 +1242,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G14" s="8">
         <v>480</v>
@@ -1239,7 +1257,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
@@ -1248,25 +1266,25 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="G15" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>19</v>
@@ -1275,7 +1293,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
@@ -1284,10 +1302,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1296,13 +1314,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G16" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>19</v>
@@ -1311,7 +1329,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1320,10 +1338,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
@@ -1332,10 +1350,10 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G17" s="8">
         <v>480</v>
@@ -1347,7 +1365,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1356,22 +1374,22 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G18" s="8">
         <v>480</v>
@@ -1383,7 +1401,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
@@ -1392,10 +1410,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>15</v>
@@ -1419,7 +1437,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1428,10 +1446,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -1440,10 +1458,10 @@
         <v>16</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" s="8">
         <v>480</v>
@@ -1455,7 +1473,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
@@ -1464,10 +1482,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1476,13 +1494,13 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G21" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>19</v>
@@ -1491,7 +1509,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1500,10 +1518,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1512,13 +1530,13 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G22" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>19</v>
@@ -1527,7 +1545,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1536,10 +1554,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1548,13 +1566,13 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="G23" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>19</v>
@@ -1563,7 +1581,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
@@ -1572,34 +1590,34 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="8">
+        <v>90</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="8">
-        <v>90</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -1608,34 +1626,34 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="8">
+        <v>90</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="8">
-        <v>90</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -1644,34 +1662,34 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="8">
+        <v>90</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" s="8">
-        <v>90</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -1680,23 +1698,23 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="G27" s="8">
         <v>90</v>
       </c>
@@ -1707,7 +1725,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -1716,25 +1734,25 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="F28" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="G28" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>19</v>
@@ -1752,10 +1770,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -1779,19 +1797,19 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -1800,10 +1818,10 @@
         <v>16</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="4">
         <v>90</v>
@@ -1815,7 +1833,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -1824,10 +1842,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -1836,13 +1854,13 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G31" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>19</v>
@@ -1860,10 +1878,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -1872,13 +1890,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="G32" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>19</v>
@@ -1887,7 +1905,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -1896,25 +1914,25 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="F33" s="4" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="G33" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>19</v>
@@ -1923,7 +1941,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
@@ -1932,10 +1950,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -1944,13 +1962,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="G34" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>19</v>
@@ -1959,7 +1977,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -1968,10 +1986,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -1980,13 +1998,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="G35" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>19</v>
@@ -1995,7 +2013,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2004,10 +2022,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2016,10 +2034,10 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G36" s="4">
         <v>90</v>
@@ -2031,7 +2049,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
@@ -2040,10 +2058,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2052,13 +2070,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="G37" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>19</v>
@@ -2067,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2076,10 +2094,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2088,13 +2106,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="G38" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>19</v>
@@ -2103,7 +2121,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2112,10 +2130,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -2124,13 +2142,13 @@
         <v>16</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="G39" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>19</v>
@@ -2139,7 +2157,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
@@ -2148,10 +2166,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -2163,7 +2181,7 @@
         <v>24</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G40" s="4">
         <v>480</v>
@@ -2175,7 +2193,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2184,10 +2202,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -2196,13 +2214,13 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="G41" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>19</v>
@@ -2211,7 +2229,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
@@ -2220,10 +2238,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2232,13 +2250,13 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G42" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>19</v>
@@ -2247,7 +2265,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2256,10 +2274,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -2268,13 +2286,13 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="G43" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>19</v>
@@ -2283,7 +2301,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2292,10 +2310,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
@@ -2304,10 +2322,10 @@
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G44" s="4">
         <v>90</v>
@@ -2319,7 +2337,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
@@ -2328,10 +2346,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
@@ -2340,10 +2358,10 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="G45" s="4">
         <v>90</v>
@@ -2355,7 +2373,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2364,10 +2382,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -2376,10 +2394,10 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G46" s="4">
         <v>90</v>
@@ -2391,7 +2409,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
@@ -2400,10 +2418,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -2412,10 +2430,10 @@
         <v>16</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="G47" s="4">
         <v>90</v>
@@ -2427,7 +2445,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
@@ -2436,10 +2454,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
@@ -2448,10 +2466,10 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G48" s="4">
         <v>90</v>
@@ -2463,7 +2481,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2472,10 +2490,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
@@ -2484,13 +2502,13 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="G49" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>19</v>
@@ -2499,7 +2517,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2508,10 +2526,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -2520,10 +2538,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G50" s="4">
         <v>90</v>
@@ -2535,10 +2553,82 @@
         <v>20</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="4">
+        <v>90</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="4">
+        <v>480</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="4" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -70,135 +70,165 @@
     <t>Pulverize</t>
   </si>
   <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
     <t>19/09/2026 06:00:00</t>
   </si>
   <si>
     <t>19/09/2026 14:00:00</t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>02644057</t>
   </si>
   <si>
     <t>Phạm Văn Công</t>
   </si>
   <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>25/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
     <t>12/09/2026 06:00:00</t>
   </si>
   <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
-  </si>
-  <si>
     <t>Sai giờ</t>
   </si>
   <si>
     <t>Từ chối</t>
   </si>
   <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>Tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>21/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>24/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chuẩn bị kiểm kê </t>
-  </si>
-  <si>
-    <t>23/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">Tăng cường sản xuất </t>
   </si>
   <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>lắp đặt thiết bị</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
     <t>19/09/2026 07:45:00</t>
   </si>
   <si>
@@ -208,21 +238,6 @@
     <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
     <t>16/09/2026 20:30:00</t>
   </si>
   <si>
@@ -235,12 +250,6 @@
     <t>18/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>22/09/2026 12:30:00</t>
   </si>
   <si>
@@ -262,15 +271,18 @@
     <t xml:space="preserve">tăng cường sản xuất </t>
   </si>
   <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
     <t>24/09/2026 20:30:00</t>
   </si>
   <si>
     <t>24/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
     <t>23/09/2026 20:30:00</t>
   </si>
   <si>
@@ -289,85 +301,82 @@
     <t>22/09/2026 22:00:00</t>
   </si>
   <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>16/09/2026 14:00:00</t>
   </si>
   <si>
     <t>16/09/2026 15:30:00</t>
   </si>
   <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
     <t>15/09/2026 14:00:00</t>
   </si>
   <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
     <t>15/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>Tăng Cường Sản Xuất</t>
-  </si>
-  <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
   </si>
 </sst>
 </file>
@@ -868,10 +877,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>15</v>
@@ -880,10 +889,10 @@
         <v>16</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G4" s="8">
         <v>480</v>
@@ -895,7 +904,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
@@ -904,63 +913,61 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="8">
+        <v>480</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="8">
-        <v>435</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>19</v>
@@ -969,7 +976,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
@@ -978,10 +985,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -990,10 +997,10 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G7" s="8">
         <v>90</v>
@@ -1005,7 +1012,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -1014,10 +1021,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
@@ -1026,13 +1033,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G8" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>19</v>
@@ -1041,7 +1048,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1050,10 +1057,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -1062,22 +1069,22 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8">
+        <v>90</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="G9" s="8">
-        <v>90</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1086,10 +1093,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -1104,7 +1111,7 @@
         <v>41</v>
       </c>
       <c r="G10" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
@@ -1113,19 +1120,19 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -1134,13 +1141,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G11" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>19</v>
@@ -1149,7 +1156,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1158,10 +1165,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -1170,10 +1177,10 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G12" s="8">
         <v>90</v>
@@ -1185,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1194,10 +1201,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1206,10 +1213,10 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" s="8">
         <v>90</v>
@@ -1221,7 +1228,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1230,10 +1237,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1242,10 +1249,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G14" s="8">
         <v>480</v>
@@ -1257,7 +1264,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
@@ -1266,10 +1273,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
@@ -1278,10 +1285,10 @@
         <v>16</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G15" s="8">
         <v>90</v>
@@ -1293,7 +1300,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
@@ -1302,11 +1309,11 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
@@ -1314,10 +1321,10 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G16" s="8">
         <v>480</v>
@@ -1329,7 +1336,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1338,10 +1345,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
@@ -1350,10 +1357,10 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G17" s="8">
         <v>480</v>
@@ -1365,7 +1372,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1374,10 +1381,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1386,10 +1393,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G18" s="8">
         <v>480</v>
@@ -1401,7 +1408,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
@@ -1410,10 +1417,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>15</v>
@@ -1422,10 +1429,10 @@
         <v>16</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G19" s="8">
         <v>90</v>
@@ -1437,7 +1444,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1446,10 +1453,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -1458,13 +1465,13 @@
         <v>16</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="G20" s="8">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>19</v>
@@ -1473,19 +1480,21 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="K20" s="7"/>
+        <v>32</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="L20" s="8" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1494,10 +1503,10 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G21" s="8">
         <v>90</v>
@@ -1509,7 +1518,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1518,10 +1527,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1530,10 +1539,10 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G22" s="8">
         <v>480</v>
@@ -1545,7 +1554,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1554,10 +1563,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1566,10 +1575,10 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G23" s="8">
         <v>480</v>
@@ -1581,7 +1590,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
@@ -1590,10 +1599,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -1602,13 +1611,13 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>19</v>
@@ -1617,7 +1626,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -1626,10 +1635,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>15</v>
@@ -1638,13 +1647,13 @@
         <v>16</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G25" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>19</v>
@@ -1653,7 +1662,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -1662,10 +1671,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
@@ -1674,10 +1683,10 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G26" s="8">
         <v>90</v>
@@ -1689,7 +1698,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -1698,10 +1707,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
@@ -1710,10 +1719,10 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" s="8">
         <v>90</v>
@@ -1725,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -1734,23 +1743,23 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="G28" s="8">
         <v>90</v>
       </c>
@@ -1761,7 +1770,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
@@ -1770,10 +1779,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -1797,19 +1806,19 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -1833,7 +1842,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -1842,10 +1851,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -1869,7 +1878,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
@@ -1878,10 +1887,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -1890,13 +1899,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G32" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>19</v>
@@ -1905,7 +1914,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -1914,10 +1923,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
@@ -1926,10 +1935,10 @@
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G33" s="4">
         <v>90</v>
@@ -1941,7 +1950,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
@@ -1950,10 +1959,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -1962,13 +1971,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="G34" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>19</v>
@@ -1977,7 +1986,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -1986,10 +1995,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -1998,13 +2007,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="G35" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>19</v>
@@ -2013,7 +2022,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2022,10 +2031,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2034,10 +2043,10 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="4">
         <v>90</v>
@@ -2049,7 +2058,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
@@ -2058,10 +2067,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2070,10 +2079,10 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G37" s="4">
         <v>90</v>
@@ -2085,7 +2094,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2094,10 +2103,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2106,13 +2115,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="G38" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>19</v>
@@ -2121,7 +2130,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2145,7 +2154,7 @@
         <v>18</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G39" s="4">
         <v>480</v>
@@ -2166,10 +2175,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -2178,10 +2187,10 @@
         <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G40" s="4">
         <v>480</v>
@@ -2193,7 +2202,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2214,10 +2223,10 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G41" s="4">
         <v>480</v>
@@ -2238,10 +2247,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2250,13 +2259,13 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="G42" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>19</v>
@@ -2265,7 +2274,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2286,10 +2295,10 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G43" s="4">
         <v>480</v>
@@ -2301,7 +2310,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2322,26 +2331,26 @@
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G44" s="4">
+        <v>90</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G44" s="4">
-        <v>90</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
@@ -2358,10 +2367,10 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G45" s="4">
         <v>90</v>
@@ -2373,7 +2382,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2394,7 +2403,7 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>110</v>
@@ -2409,7 +2418,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
@@ -2433,7 +2442,7 @@
         <v>111</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G47" s="4">
         <v>90</v>
@@ -2445,7 +2454,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
@@ -2466,10 +2475,10 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G48" s="4">
         <v>90</v>
@@ -2481,7 +2490,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2502,10 +2511,10 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G49" s="4">
         <v>90</v>
@@ -2517,7 +2526,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2538,10 +2547,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="G50" s="4">
         <v>90</v>
@@ -2553,7 +2562,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
@@ -2577,7 +2586,7 @@
         <v>116</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="G51" s="4">
         <v>90</v>
@@ -2589,7 +2598,7 @@
         <v>20</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="4" t="s">
@@ -2613,7 +2622,7 @@
         <v>18</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G52" s="4">
         <v>480</v>
@@ -2625,10 +2634,82 @@
         <v>20</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="4">
+        <v>90</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="4">
+        <v>480</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="4" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -58,91 +58,217 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>27/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Sai giờ</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>26/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>02223526</t>
   </si>
   <si>
     <t>Nguyễn Thiên Phú</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>26/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>27/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu </t>
+  </si>
+  <si>
+    <t>29/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">Tăng cường sản xuất </t>
   </si>
   <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
-  </si>
-  <si>
-    <t>Sai giờ</t>
-  </si>
-  <si>
-    <t>Từ chối</t>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
   </si>
   <si>
     <t>17/09/2026 20:30:00</t>
@@ -151,16 +277,31 @@
     <t>17/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
+    <t>22/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
   </si>
   <si>
     <t>02243654</t>
@@ -169,193 +310,91 @@
     <t>Lưu Văn Giang</t>
   </si>
   <si>
-    <t>26/09/2026 06:00:00</t>
-  </si>
-  <si>
     <t>Tăng Cường Sản Xuất</t>
   </si>
   <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>22/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>02622116</t>
   </si>
   <si>
     <t>Trịnh Nhựt Khánh</t>
   </si>
   <si>
-    <t>25/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>25/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
     <t>02644066</t>
   </si>
   <si>
     <t>Nguyễn Hữu Tình</t>
   </si>
   <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
     <t>18/09/2026 12:30:00</t>
   </si>
   <si>
     <t>18/09/2026 14:00:00</t>
   </si>
   <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>25/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>lắp đặt thiết bị</t>
-  </si>
-  <si>
-    <t>26/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu </t>
-  </si>
-  <si>
-    <t>24/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chuẩn bị kiểm kê </t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
+    <t>24/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
   </si>
   <si>
     <t>25/09/2026 20:30:00</t>
@@ -364,43 +403,13 @@
     <t>25/09/2026 22:30:00</t>
   </si>
   <si>
-    <t>24/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 22:00:00</t>
+    <t>17/09/2026 15:30:00</t>
   </si>
   <si>
     <t>21/09/2026 20:30:00</t>
   </si>
   <si>
     <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -901,22 +910,22 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="G4" s="8">
         <v>480</v>
@@ -928,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
@@ -949,10 +958,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="8">
         <v>480</v>
@@ -964,7 +973,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
@@ -973,10 +982,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>15</v>
@@ -985,10 +994,10 @@
         <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G6" s="8">
         <v>480</v>
@@ -1000,7 +1009,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
@@ -1009,10 +1018,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -1021,13 +1030,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>19</v>
@@ -1036,7 +1045,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -1045,22 +1054,22 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="8">
         <v>480</v>
@@ -1072,7 +1081,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1081,25 +1090,25 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="G9" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>19</v>
@@ -1108,7 +1117,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1117,10 +1126,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -1129,13 +1138,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10" s="8">
-        <v>435</v>
+        <v>480</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
@@ -1144,45 +1153,43 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="8">
+        <v>90</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="8">
-        <v>90</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1191,10 +1198,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -1203,22 +1210,22 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="8">
+        <v>90</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="8">
-        <v>90</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1227,10 +1234,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1239,22 +1246,22 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8">
+        <v>480</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="G13" s="8">
-        <v>90</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1263,10 +1270,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1275,13 +1282,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G14" s="8">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>19</v>
@@ -1290,19 +1297,21 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="L14" s="8" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
@@ -1311,10 +1320,10 @@
         <v>16</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G15" s="8">
         <v>480</v>
@@ -1326,7 +1335,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
@@ -1335,10 +1344,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1347,10 +1356,10 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G16" s="8">
         <v>480</v>
@@ -1362,7 +1371,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1371,10 +1380,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
@@ -1383,13 +1392,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="G17" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>19</v>
@@ -1398,7 +1407,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1407,10 +1416,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1419,10 +1428,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G18" s="8">
         <v>480</v>
@@ -1434,7 +1443,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
@@ -1443,10 +1452,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>15</v>
@@ -1455,13 +1464,13 @@
         <v>16</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G19" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>19</v>
@@ -1470,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1479,10 +1488,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -1491,13 +1500,13 @@
         <v>16</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="G20" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>19</v>
@@ -1506,7 +1515,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
@@ -1515,10 +1524,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1527,13 +1536,13 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G21" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>19</v>
@@ -1542,7 +1551,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1551,10 +1560,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1563,10 +1572,10 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G22" s="8">
         <v>480</v>
@@ -1578,7 +1587,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1587,10 +1596,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1599,34 +1608,34 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="8">
+        <v>90</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="8">
-        <v>480</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -1635,13 +1644,13 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G24" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>19</v>
@@ -1650,7 +1659,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -1659,22 +1668,22 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="F25" s="8" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G25" s="8">
         <v>480</v>
@@ -1686,7 +1695,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -1695,10 +1704,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
@@ -1707,10 +1716,10 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G26" s="8">
         <v>90</v>
@@ -1722,7 +1731,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -1731,10 +1740,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
@@ -1743,13 +1752,13 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="G27" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>19</v>
@@ -1758,7 +1767,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -1767,10 +1776,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>15</v>
@@ -1779,13 +1788,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G28" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>19</v>
@@ -1794,7 +1803,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
@@ -1803,10 +1812,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -1815,13 +1824,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="G29" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>19</v>
@@ -1830,7 +1839,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
@@ -1839,10 +1848,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -1851,13 +1860,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="G30" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>19</v>
@@ -1866,7 +1875,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -1875,10 +1884,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -1887,13 +1896,13 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="G31" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>19</v>
@@ -1902,7 +1911,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
@@ -1911,10 +1920,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -1923,10 +1932,10 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="G32" s="4">
         <v>90</v>
@@ -1938,7 +1947,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -1947,10 +1956,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
@@ -1959,13 +1968,13 @@
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G33" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>19</v>
@@ -1974,7 +1983,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
@@ -1983,10 +1992,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -1995,13 +2004,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="G34" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>19</v>
@@ -2010,7 +2019,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -2019,10 +2028,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -2031,13 +2040,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="G35" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>19</v>
@@ -2046,7 +2055,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2055,10 +2064,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2067,13 +2076,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G36" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>19</v>
@@ -2082,7 +2091,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
@@ -2091,10 +2100,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2103,10 +2112,10 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G37" s="4">
         <v>90</v>
@@ -2118,7 +2127,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2127,10 +2136,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2139,13 +2148,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G38" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>19</v>
@@ -2154,7 +2163,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2163,10 +2172,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -2175,10 +2184,10 @@
         <v>16</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G39" s="4">
         <v>480</v>
@@ -2190,7 +2199,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
@@ -2199,10 +2208,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -2211,13 +2220,13 @@
         <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="G40" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>19</v>
@@ -2226,7 +2235,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2235,10 +2244,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -2247,13 +2256,13 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="G41" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>19</v>
@@ -2262,7 +2271,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
@@ -2271,10 +2280,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2283,13 +2292,13 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="G42" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>19</v>
@@ -2298,7 +2307,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2307,10 +2316,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -2319,13 +2328,13 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="G43" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>19</v>
@@ -2334,7 +2343,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2343,10 +2352,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
@@ -2355,10 +2364,10 @@
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G44" s="4">
         <v>90</v>
@@ -2370,7 +2379,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
@@ -2379,10 +2388,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
@@ -2391,10 +2400,10 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="G45" s="4">
         <v>90</v>
@@ -2406,7 +2415,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2415,10 +2424,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -2427,13 +2436,13 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="G46" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>19</v>
@@ -2442,7 +2451,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
@@ -2451,10 +2460,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -2463,13 +2472,13 @@
         <v>16</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G47" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>19</v>
@@ -2478,7 +2487,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
@@ -2487,10 +2496,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
@@ -2499,13 +2508,13 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G48" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>19</v>
@@ -2514,7 +2523,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2523,10 +2532,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
@@ -2535,10 +2544,10 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G49" s="4">
         <v>90</v>
@@ -2550,7 +2559,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2559,10 +2568,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -2571,10 +2580,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G50" s="4">
         <v>90</v>
@@ -2586,7 +2595,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
@@ -2595,10 +2604,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>15</v>
@@ -2607,22 +2616,22 @@
         <v>16</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G51" s="4">
+        <v>90</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="G51" s="4">
-        <v>90</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="4" t="s">
@@ -2631,10 +2640,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -2643,10 +2652,10 @@
         <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="G52" s="4">
         <v>480</v>
@@ -2658,7 +2667,7 @@
         <v>20</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="4" t="s">
@@ -2667,10 +2676,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
@@ -2679,10 +2688,10 @@
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G53" s="4">
         <v>90</v>
@@ -2694,7 +2703,7 @@
         <v>20</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="4" t="s">
@@ -2703,10 +2712,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>15</v>
@@ -2715,10 +2724,10 @@
         <v>16</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="G54" s="4">
         <v>480</v>
@@ -2730,7 +2739,7 @@
         <v>20</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="4" t="s">
@@ -2739,10 +2748,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
@@ -2751,22 +2760,22 @@
         <v>16</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="F55" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G55" s="4">
+        <v>480</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="G55" s="4">
-        <v>90</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="4" t="s">
@@ -2775,10 +2784,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
@@ -2787,13 +2796,13 @@
         <v>16</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="G56" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>19</v>
@@ -2802,7 +2811,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="4" t="s">
@@ -2811,10 +2820,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -2823,10 +2832,10 @@
         <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G57" s="4">
         <v>90</v>
@@ -2838,7 +2847,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="4" t="s">
@@ -2847,10 +2856,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
@@ -2859,10 +2868,10 @@
         <v>16</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G58" s="4">
         <v>90</v>
@@ -2874,7 +2883,7 @@
         <v>20</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="4" t="s">
@@ -2883,10 +2892,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
@@ -2895,10 +2904,10 @@
         <v>16</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G59" s="4">
         <v>480</v>
@@ -2910,7 +2919,7 @@
         <v>20</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="4" t="s">
@@ -2919,10 +2928,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
@@ -2931,10 +2940,10 @@
         <v>16</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G60" s="4">
         <v>90</v>
@@ -2946,7 +2955,7 @@
         <v>20</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="4" t="s">
@@ -2955,10 +2964,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -2967,10 +2976,10 @@
         <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G61" s="4">
         <v>90</v>
@@ -2982,7 +2991,7 @@
         <v>20</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="4" t="s">
@@ -2991,10 +3000,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
@@ -3003,10 +3012,10 @@
         <v>16</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G62" s="4">
         <v>90</v>
@@ -3018,7 +3027,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="4" t="s">
@@ -3027,10 +3036,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
@@ -3039,13 +3048,13 @@
         <v>16</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="G63" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>19</v>
@@ -3054,7 +3063,7 @@
         <v>20</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="4" t="s">
@@ -3063,10 +3072,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -3075,10 +3084,10 @@
         <v>16</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G64" s="4">
         <v>90</v>
@@ -3090,7 +3099,7 @@
         <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="4" t="s">
@@ -3099,10 +3108,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
@@ -3111,10 +3120,10 @@
         <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G65" s="4">
         <v>90</v>
@@ -3126,10 +3135,46 @@
         <v>20</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" s="4">
+        <v>480</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="4" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -58,16 +58,139 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>27/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>26/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
   </si>
   <si>
     <t>02/10/2026 16:30:00</t>
@@ -76,16 +199,223 @@
     <t>02/10/2026 18:00:00</t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
     <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
+    <t>29/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu </t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>Sai giờ</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>24/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 22:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -568,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -585,368 +915,2310 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="A4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="8">
+        <v>480</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
+      <c r="L4" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="8">
+        <v>480</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="K5" s="7"/>
-      <c r="L5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="8">
+        <v>480</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="K6" s="7"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="8">
+        <v>480</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
+      <c r="L7" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="8">
+        <v>480</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="8">
+        <v>90</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="A10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="8">
+        <v>480</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="8">
+        <v>480</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="K11" s="7"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="A12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="8">
+        <v>480</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="13" s="2" customFormat="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
+      <c r="A13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="8">
+        <v>90</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="K13" s="7"/>
-      <c r="L13" s="8"/>
+      <c r="L13" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="8">
+        <v>480</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="K14" s="7"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="8">
+        <v>480</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="K15" s="7"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="8">
+        <v>90</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="K16" s="7"/>
-      <c r="L16" s="8"/>
+      <c r="L16" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="8">
+        <v>480</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K17" s="7"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="8">
+        <v>90</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="K18" s="7"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="8">
+        <v>480</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K19" s="7"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="A20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="8">
+        <v>90</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="K20" s="7"/>
-      <c r="L20" s="8"/>
+      <c r="L20" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="8">
+        <v>480</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K21" s="7"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="8">
+        <v>480</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="K22" s="7"/>
-      <c r="L22" s="8"/>
+      <c r="L22" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
+      <c r="A23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="8">
+        <v>480</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K23" s="7"/>
-      <c r="L23" s="8"/>
+      <c r="L23" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="8">
+        <v>90</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="K24" s="7"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
+      <c r="A25" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="8">
+        <v>480</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="K25" s="7"/>
-      <c r="L25" s="8"/>
+      <c r="L25" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
+      <c r="A26" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="8">
+        <v>480</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K26" s="7"/>
-      <c r="L26" s="8"/>
+      <c r="L26" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="8">
+        <v>480</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="K27" s="7"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
+      <c r="A28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="8">
+        <v>480</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K28" s="7"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
+      <c r="A29" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="8">
+        <v>90</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="K29" s="7"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="4">
+        <v>90</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="4">
+        <v>90</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="4">
+        <v>90</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="4">
+        <v>90</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="4">
+        <v>90</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="4">
+        <v>480</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="4">
+        <v>90</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G37" s="4">
+        <v>90</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="4">
+        <v>480</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="4">
+        <v>480</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="4">
+        <v>480</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="4">
+        <v>435</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="4">
+        <v>90</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="4">
+        <v>480</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G44" s="4">
+        <v>90</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="4">
+        <v>480</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G46" s="4">
+        <v>90</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G47" s="4">
+        <v>90</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G48" s="4">
+        <v>90</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G49" s="4">
+        <v>90</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="4">
+        <v>90</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" s="4">
+        <v>480</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G52" s="4">
+        <v>90</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G53" s="4">
+        <v>90</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G54" s="4">
+        <v>90</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G55" s="4">
+        <v>90</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="4">
+        <v>480</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G57" s="4">
+        <v>90</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" s="4">
+        <v>90</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G59" s="4">
+        <v>90</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G60" s="4">
+        <v>90</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G61" s="4">
+        <v>90</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G62" s="4">
+        <v>90</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G63" s="4">
+        <v>90</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K63" s="3"/>
+      <c r="L63" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G64" s="4">
+        <v>90</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="4">
+        <v>480</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K65" s="3"/>
+      <c r="L65" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" s="4">
+        <v>480</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G67" s="4">
+        <v>90</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -82,7 +82,7 @@
     <t>Thân Trọng Tuấn</t>
   </si>
   <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+    <t>vận hành máy nghiền</t>
   </si>
   <si>
     <t>Chưa duyệt</t>
@@ -112,6 +112,63 @@
     <t>09/10/2026 22:00:00</t>
   </si>
   <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>02/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 15:30:00</t>
+  </si>
+  <si>
     <t>02644075</t>
   </si>
   <si>
@@ -121,76 +178,19 @@
     <t>05/10/2026 12:30:00</t>
   </si>
   <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
+    <t xml:space="preserve">vận hành máy nghiền </t>
   </si>
   <si>
     <t>07/10/2026 12:30:00</t>
   </si>
   <si>
-    <t>07/10/2026 14:00:00</t>
-  </si>
-  <si>
     <t>08/10/2026 12:30:00</t>
   </si>
   <si>
-    <t>08/10/2026 14:00:00</t>
-  </si>
-  <si>
     <t>09/10/2026 12:30:00</t>
   </si>
   <si>
-    <t>09/10/2026 14:00:00</t>
-  </si>
-  <si>
     <t>06/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>02/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02/10/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>09/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -866,15 +866,15 @@
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -883,10 +883,10 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" s="8">
         <v>90</v>
@@ -898,7 +898,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -907,10 +907,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -919,10 +919,10 @@
         <v>16</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G10" s="8">
         <v>90</v>
@@ -934,7 +934,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -943,10 +943,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -955,22 +955,22 @@
         <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="8">
+        <v>90</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G11" s="8">
-        <v>90</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -979,10 +979,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -991,10 +991,10 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G12" s="8">
         <v>90</v>
@@ -1006,7 +1006,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1027,10 +1027,10 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" s="8">
         <v>90</v>
@@ -1042,11 +1042,11 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
@@ -1063,10 +1063,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G14" s="8">
         <v>90</v>
@@ -1099,10 +1099,10 @@
         <v>16</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G15" s="8">
         <v>90</v>
@@ -1135,10 +1135,10 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G16" s="8">
         <v>90</v>
@@ -1171,10 +1171,10 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G17" s="8">
         <v>90</v>
@@ -1207,10 +1207,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G18" s="8">
         <v>90</v>

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -85,15 +85,18 @@
     <t>vận hành máy nghiền</t>
   </si>
   <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>06/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 22:00:00</t>
+  </si>
+  <si>
     <t>Chưa duyệt</t>
   </si>
   <si>
-    <t>06/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 22:00:00</t>
-  </si>
-  <si>
     <t>07/10/2026 20:30:00</t>
   </si>
   <si>
@@ -106,28 +109,25 @@
     <t>08/10/2026 22:00:00</t>
   </si>
   <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>02/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
     <t>09/10/2026 20:30:00</t>
   </si>
   <si>
     <t>09/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>02/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02/10/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
   </si>
   <si>
     <t>02644066</t>
@@ -722,7 +722,7 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
@@ -739,10 +739,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="8">
         <v>90</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
@@ -775,10 +775,10 @@
         <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="8">
         <v>90</v>
@@ -794,15 +794,15 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -811,10 +811,10 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G7" s="8">
         <v>90</v>
@@ -826,7 +826,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -835,10 +835,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
@@ -847,10 +847,10 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" s="8">
         <v>90</v>
@@ -862,11 +862,11 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
@@ -938,7 +938,7 @@
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
@@ -974,7 +974,7 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -94,21 +94,42 @@
     <t>06/10/2026 22:00:00</t>
   </si>
   <si>
+    <t>07/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 22:00:00</t>
+  </si>
+  <si>
     <t>Chưa duyệt</t>
   </si>
   <si>
-    <t>07/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 22:00:00</t>
-  </si>
-  <si>
     <t>08/10/2026 20:30:00</t>
   </si>
   <si>
     <t>08/10/2026 22:00:00</t>
   </si>
   <si>
+    <t>09/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
@@ -124,73 +145,52 @@
     <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
-    <t>09/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
     <t>09/10/2026 14:00:00</t>
   </si>
   <si>
     <t>09/10/2026 15:30:00</t>
   </si>
   <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>07/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
+  </si>
+  <si>
     <t>06/10/2026 14:00:00</t>
   </si>
   <si>
     <t>06/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>07/10/2026 14:00:00</t>
-  </si>
-  <si>
     <t>07/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>08/10/2026 14:00:00</t>
-  </si>
-  <si>
     <t>08/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>05/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận hành máy nghiền </t>
-  </si>
-  <si>
-    <t>07/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 12:30:00</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
@@ -739,10 +739,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="G5" s="8">
         <v>90</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
@@ -794,28 +794,28 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="G7" s="8">
         <v>90</v>
       </c>
@@ -826,19 +826,19 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
@@ -847,26 +847,26 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8">
+        <v>90</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="G8" s="8">
-        <v>90</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
@@ -907,10 +907,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -934,19 +934,19 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -955,10 +955,10 @@
         <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G11" s="8">
         <v>90</v>
@@ -970,19 +970,19 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -991,34 +991,34 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="8">
+        <v>90</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="G12" s="8">
-        <v>90</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1027,10 +1027,10 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" s="8">
         <v>90</v>
@@ -1042,19 +1042,19 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1066,7 +1066,7 @@
         <v>52</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G14" s="8">
         <v>90</v>
@@ -1078,19 +1078,19 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
@@ -1099,11 +1099,11 @@
         <v>16</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="G15" s="8">
         <v>90</v>
       </c>
@@ -1114,19 +1114,19 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1135,11 +1135,11 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="G16" s="8">
         <v>90</v>
       </c>
@@ -1150,19 +1150,19 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
@@ -1171,11 +1171,11 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="G17" s="8">
         <v>90</v>
       </c>
@@ -1186,32 +1186,32 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="G18" s="8">
         <v>90</v>
       </c>
@@ -1222,11 +1222,11 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -58,16 +58,79 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>10/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
     <t>02644057</t>
   </si>
   <si>
     <t>Phạm Văn Công</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
+    <t>09/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>02/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
     <t>05/10/2026 20:30:00</t>
@@ -76,58 +139,67 @@
     <t>05/10/2026 22:00:00</t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>vận hành máy nghiền</t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
     <t>06/10/2026 20:30:00</t>
   </si>
   <si>
     <t>06/10/2026 22:00:00</t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
     <t>07/10/2026 20:30:00</t>
   </si>
   <si>
     <t>07/10/2026 22:00:00</t>
   </si>
   <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
     <t>08/10/2026 20:30:00</t>
   </si>
   <si>
     <t>08/10/2026 22:00:00</t>
   </si>
   <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>02/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02/10/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>09/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 22:00:00</t>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>10/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>07/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
   </si>
   <si>
     <t>02644066</t>
@@ -136,61 +208,34 @@
     <t>Nguyễn Hữu Tình</t>
   </si>
   <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
     <t>05/10/2026 14:00:00</t>
   </si>
   <si>
     <t>05/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>09/10/2026 14:00:00</t>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 15:30:00</t>
   </si>
   <si>
     <t>09/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>05/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận hành máy nghiền </t>
-  </si>
-  <si>
-    <t>07/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 12:30:00</t>
   </si>
 </sst>
 </file>
@@ -673,7 +718,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -691,10 +736,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>15</v>
@@ -703,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G4" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>19</v>
@@ -718,19 +763,19 @@
         <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>15</v>
@@ -739,10 +784,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8">
         <v>90</v>
@@ -754,19 +799,19 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>15</v>
@@ -775,10 +820,10 @@
         <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G6" s="8">
         <v>90</v>
@@ -790,19 +835,19 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -811,10 +856,10 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G7" s="8">
         <v>90</v>
@@ -826,19 +871,19 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
@@ -847,10 +892,10 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G8" s="8">
         <v>90</v>
@@ -862,19 +907,19 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -883,10 +928,10 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8">
         <v>90</v>
@@ -898,19 +943,19 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -919,13 +964,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="G10" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
@@ -934,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -955,10 +1000,10 @@
         <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G11" s="8">
         <v>90</v>
@@ -970,19 +1015,19 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -991,13 +1036,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G12" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>19</v>
@@ -1006,19 +1051,19 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1027,13 +1072,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G13" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>19</v>
@@ -1042,19 +1087,19 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1063,10 +1108,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G14" s="8">
         <v>90</v>
@@ -1078,19 +1123,19 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
@@ -1099,10 +1144,10 @@
         <v>16</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G15" s="8">
         <v>90</v>
@@ -1114,19 +1159,19 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1135,10 +1180,10 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G16" s="8">
         <v>90</v>
@@ -1150,34 +1195,34 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="F17" s="8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G17" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>19</v>
@@ -1186,19 +1231,19 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1207,10 +1252,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G18" s="8">
         <v>90</v>
@@ -1222,96 +1267,228 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="8">
+        <v>90</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="K19" s="7"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="A20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="8">
+        <v>90</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="K20" s="7"/>
-      <c r="L20" s="8"/>
+      <c r="L20" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="8">
+        <v>90</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="K21" s="7"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="8">
+        <v>90</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="K22" s="7"/>
-      <c r="L22" s="8"/>
+      <c r="L22" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
+      <c r="A23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="8">
+        <v>90</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="K23" s="7"/>
-      <c r="L23" s="8"/>
+      <c r="L23" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="8">
+        <v>90</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="K24" s="7"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7"/>

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -58,184 +58,238 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>02/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>05/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>06/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>10/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
     <t>02222350</t>
   </si>
   <si>
     <t>Hoàng Văn Nguyên</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>10/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>11/10/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
     <t>Tăng cường sản xuất</t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
     <t>02121404</t>
   </si>
   <si>
     <t>Lê Hoàng Minh Tâm</t>
   </si>
   <si>
-    <t>10/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>09/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>vận hành máy nghiền</t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>02/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02/10/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>05/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>Tăng Cường Sản Xuất</t>
-  </si>
-  <si>
-    <t>08/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
-  </si>
-  <si>
-    <t>10/10/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận hành máy nghiền </t>
-  </si>
-  <si>
-    <t>07/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>06/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 15:30:00</t>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>12/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tǎng ca Vân hành máy nghiên</t>
+  </si>
+  <si>
+    <t>12/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca Vân hành máy nghiêń</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>14/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -718,7 +772,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -751,10 +805,10 @@
         <v>25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G4" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>19</v>
@@ -763,7 +817,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
@@ -772,10 +826,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>15</v>
@@ -784,10 +838,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G5" s="8">
         <v>90</v>
@@ -803,51 +857,51 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8">
+        <v>90</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="G6" s="8">
-        <v>90</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -856,11 +910,11 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="G7" s="8">
         <v>90</v>
       </c>
@@ -871,19 +925,19 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
@@ -892,11 +946,11 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="G8" s="8">
         <v>90</v>
       </c>
@@ -907,19 +961,19 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -928,11 +982,11 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="G9" s="8">
         <v>90</v>
       </c>
@@ -943,34 +997,34 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="G10" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
@@ -979,7 +1033,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -988,10 +1042,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -1000,10 +1054,10 @@
         <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G11" s="8">
         <v>90</v>
@@ -1019,15 +1073,15 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -1036,13 +1090,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G12" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>19</v>
@@ -1051,7 +1105,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1060,10 +1114,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1072,13 +1126,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>19</v>
@@ -1087,7 +1141,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1096,10 +1150,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1108,10 +1162,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G14" s="8">
         <v>90</v>
@@ -1123,32 +1177,32 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="G15" s="8">
         <v>90</v>
       </c>
@@ -1159,19 +1213,19 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1180,10 +1234,10 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G16" s="8">
         <v>90</v>
@@ -1195,19 +1249,19 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
@@ -1216,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G17" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>19</v>
@@ -1231,7 +1285,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1240,23 +1294,23 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="G18" s="8">
         <v>90</v>
       </c>
@@ -1267,55 +1321,55 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="8">
+        <v>480</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="8">
-        <v>90</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -1324,13 +1378,13 @@
         <v>16</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G20" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>19</v>
@@ -1339,34 +1393,34 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="F21" s="8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G21" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>19</v>
@@ -1375,19 +1429,19 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1396,13 +1450,13 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G22" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>19</v>
@@ -1411,19 +1465,19 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1432,13 +1486,13 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G23" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>19</v>
@@ -1447,19 +1501,19 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -1468,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G24" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>19</v>
@@ -1483,82 +1537,372 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1">
+      <c r="A25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="8">
+        <v>480</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1">
+      <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="8"/>
-    </row>
-    <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
+      <c r="B26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="8">
+        <v>480</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="K26" s="7"/>
-      <c r="L26" s="8"/>
+      <c r="L26" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="8">
+        <v>90</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="K27" s="7"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
+      <c r="A28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="8">
+        <v>90</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="K28" s="7"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
+      <c r="A29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="8">
+        <v>90</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="K29" s="7"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="4">
+        <v>90</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="4">
+        <v>90</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="4">
+        <v>90</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="4">
+        <v>90</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" s="4">
+        <v>90</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="4" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_plan_2.xlsx
+++ b/data/hrm_sync_plan_2.xlsx
@@ -280,9 +280,6 @@
     <t>tăng ca Vân hành máy nghiêń</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
     <t>14/10/2026 12:30:00</t>
   </si>
   <si>
@@ -290,6 +287,84 @@
   </si>
   <si>
     <t>14/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Làm sai giờ </t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>17/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>vận chuyển nguyên vật liệu</t>
+  </si>
+  <si>
+    <t>24/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>24/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>24/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>25/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>24/10/2026 02:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu </t>
   </si>
 </sst>
 </file>
@@ -1829,7 +1904,7 @@
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -1846,10 +1921,10 @@
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G33" s="4">
         <v>90</v>
@@ -1865,7 +1940,7 @@
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1882,10 +1957,10 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="G34" s="4">
         <v>90</v>
@@ -1901,7 +1976,801 @@
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
-        <v>87</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" s="4">
+        <v>90</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="4">
+        <v>90</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G37" s="4">
+        <v>90</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" s="4">
+        <v>90</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="4">
+        <v>90</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" s="4">
+        <v>480</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" s="4">
+        <v>480</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G42" s="4">
+        <v>480</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G43" s="4">
+        <v>480</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="4">
+        <v>480</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" s="4">
+        <v>480</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" s="4">
+        <v>480</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" s="4">
+        <v>480</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G48" s="4">
+        <v>480</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G49" s="4">
+        <v>480</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G50" s="4">
+        <v>480</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="4">
+        <v>480</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" s="4">
+        <v>480</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G53" s="4">
+        <v>480</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G54" s="4">
+        <v>480</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G55" s="4">
+        <v>960</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="4">
+        <v>480</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
